--- a/docs/full_feature_list.xlsx
+++ b/docs/full_feature_list.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ecommerce_Shop_Cosmetics\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F77C7F-C73F-4632-9C20-CA0E5A6E0E9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99B089F-F6A7-4799-AD0F-757BD17B8758}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1411,7 +1411,7 @@
         <v>60</v>
       </c>
       <c r="G24" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -2402,6 +2402,12 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A35:A39"/>
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="A15:A24"/>
+    <mergeCell ref="A25:A29"/>
+    <mergeCell ref="A30:A34"/>
     <mergeCell ref="A65:A66"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="A69:A70"/>
@@ -2412,12 +2418,6 @@
     <mergeCell ref="A57:A60"/>
     <mergeCell ref="A61:A62"/>
     <mergeCell ref="A63:A64"/>
-    <mergeCell ref="A2:A8"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="A15:A24"/>
-    <mergeCell ref="A25:A29"/>
-    <mergeCell ref="A30:A34"/>
-    <mergeCell ref="A35:A39"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
